--- a/human_validation/judge/kor/judge_D023_S001_P002__claude-sonnet-5_kor.xlsx
+++ b/human_validation/judge/kor/judge_D023_S001_P002__claude-sonnet-5_kor.xlsx
@@ -70,16 +70,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -447,7 +444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B64"/>
+  <dimension ref="A1:B56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="90" customWidth="1" min="1" max="1"/>
@@ -561,12 +558,292 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>환자 프로필</t>
+          <t>대화문</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="5" t="inlineStr">
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>[1번째 턴 · 의사 질문] 안녕하세요, 어서 오세요. 저는 [Name] 선생님입니다. 먼저, 오늘 어떤 일로 오시게 되었는지 말씀해 주시겠어요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>[1번째 턴 · 환자 응답] 거의 매일 밤 아내가 잠자리에 들고 나면, 저는 부엌에서 평소 식사량보다 훨씬 많이 먹게 돼요. 프라이드치킨, 맥앤치즈, 고구마, 롤빵... 남은 게 뭐든 다요. 접시 하나가 다 비거나, 냉장고 절반이 빌 때까지 계속 먹어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>[1번째 턴 · 의사의 감별진단] 신경성 폭식증 (D022); 폭식장애 (D023)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>[2번째 턴 · 의사 질문] 밤에 그렇게 드실 때, 완전히 깨어 있고 본인이 뭘 하는지 알고 계신가요, 아니면 완전히 깨어 있지 않은 것 같고 나중에 그걸 명확히 기억하는 데 어려움이 있으신가요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>[2번째 턴 · 환자 응답] 무슨 말씀이신지 잘 모르겠어요. 제가 부엌에서 일어나 먹고 있다는 건 아는데, 얼마나 깨어 있는지는 딱히 신경 써본 적이 없어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>[2번째 턴 · 의사의 감별진단] 신경성 폭식증 (D022); 폭식장애 (D023)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>[3번째 턴 · 의사 질문] 다음 날 아침에, 밤에 뭘 얼마나 먹었는지 명확히 기억하시나요, 아니면 누가 말해주거나 흔적을 보기 전까지는 거의, 혹은 전혀 기억이 안 나기도 하시나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>[3번째 턴 · 환자 응답] 솔직히 잘 모르겠어요. 다음 날 그걸 다 기억하는지는 별로 생각해본 적이 없어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>[3번째 턴 · 의사의 감별진단] 신경성 폭식증 (D022); 폭식장애 (D023)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" s="5" t="inlineStr">
+        <is>
+          <t>[4번째 턴 · 의사 질문] 이런 일이 일어날 때, 의식적으로 깨어나서 부엌에 가기로 결정한 걸 기억하시나요, 아니면 어떻게 갔는지도 모른 채 어느새 부엌에서 먹고 있는 자신을 발견하시나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>[4번째 턴 · 환자 응답] 잘 모르겠어요. 제가 의식적으로 일어나기로 결정하는 건지 아닌지는 딱히 신경 써본 적이 없고, 그냥 정신 차려보면 부엌에서 먹고 있더라고요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" s="5" t="inlineStr">
+        <is>
+          <t>[4번째 턴 · 의사의 감별진단] 신경성 폭식증 (D022); 폭식장애 (D023)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>[5번째 턴 · 의사 질문] 아내분이 이런 밤중 식사 중에 말을 걸거나 반응을 보려고 한 적이 있나요? 그렇다면, 완전히 깨어 있는 사람처럼 평소대로 반응하시나요, 아니면 혼란스러워 보이거나 반응이 없거나 '정신이 나가 있는' 것처럼 보이나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>[5번째 턴 · 환자 응답] 잘 모르겠어요. 그런 일이 일어나는 동안 아내가 저한테 말을 걸어본 적이 있는지에 대해서는 서로 얘기해본 적이 없어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>[5번째 턴 · 의사의 감별진단] 신경성 폭식증 (D022); 폭식장애 (D023)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="B30" s="5" t="inlineStr">
+        <is>
+          <t>[6번째 턴 · 의사 질문] 이럴 때, 낮에 완전히 깨어 있을 때처럼 부엌 불을 켜거나 접시와 식기를 사용하고 물건에 부딪히지 않고 다니실 수 있나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t>[6번째 턴 · 환자 응답] 잘 모르겠어요. 그럴 때 그런 걸 평소대로 하고 있는지는 신경 써본 적이 없어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" s="5" t="inlineStr">
+        <is>
+          <t>[6번째 턴 · 의사의 감별진단] 신경성 폭식증 (D022); 폭식장애 (D023)</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="B33" s="5" t="inlineStr">
+        <is>
+          <t>[7번째 턴 · 의사 질문] 이런 일이 일어나기 전에, 실제로 먼저 잠이 들었다가 먹으려고 깨어나시는 건가요, 아니면 아직 잠들지 않은 상태로 깨어 있다가 부엌에 가시는 건가요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="5" t="inlineStr">
+        <is>
+          <t>[7번째 턴 · 환자 응답] 솔직히 잘 모르겠어요. 부엌에 가기 전에 먼저 잠이 들었는지 아니면 계속 깨어 있었는지는 딱히 확인해본 적이 없어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="B35" s="5" t="inlineStr">
+        <is>
+          <t>[7번째 턴 · 의사의 감별진단] 신경성 폭식증 (D022); 폭식장애 (D023)</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="B36" s="5" t="inlineStr">
+        <is>
+          <t>[8번째 턴 · 의사 질문] 부엌에 가시기 전에, 배가 고파서 일어나 먹기로 선택하는 것처럼 의식적인 충동이나 식욕을 느끼시나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="5" t="inlineStr">
+        <is>
+          <t>[8번째 턴 · 환자 응답] 대부분은 아니에요, 딱히 배고프지 않아요. 아내랑 이미 저녁을 먹었을 수도 있는데, 그러고도 나중에 결국 부엌에서 남은 음식을 집어 먹다가 그게 또 한 끼가 되어버려요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="B38" s="5" t="inlineStr">
+        <is>
+          <t>[8번째 턴 · 의사의 감별진단] 신경성 폭식증 (D022); 폭식장애 (D023)</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="B39" s="5" t="inlineStr">
+        <is>
+          <t>[9번째 턴 · 의사 질문] 이런 밤중 식사 후에 감정적으로 어떤 기분이 드시나요? 속상하거나, 죄책감이 들거나, 창피하신가요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="5" t="inlineStr">
+        <is>
+          <t>[9번째 턴 · 환자 응답] 네. 끝나고 나면 제 자신이 역겨워요. 사람들은 저를 체계적이고 강한 사람으로 보는데, 저는 거기 앉아서 부끄럽고 죄책감이 들고, 또 이런 일이 일어나게 놔뒀다는 게 정말 혐오스러워요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="B41" s="5" t="inlineStr">
+        <is>
+          <t>[9번째 턴 · 의사의 감별진단] 신경성 폭식증 (D022); 폭식장애 (D023)</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="B42" s="5" t="inlineStr">
+        <is>
+          <t>[10번째 턴 · 의사 질문] 혹시 잠에서 깼을 때 부엌에 접시나 포장지, 음식이 나와 있는데 그걸 준비했거나 먹었던 기억이 전혀 없었던 적이 있나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="5" t="inlineStr">
+        <is>
+          <t>[10번째 턴 · 환자 응답] 모르겠어요. 그런 걸 본 적은 없는데, 딱히 확인해본 적도 없어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="B44" s="5" t="inlineStr">
+        <is>
+          <t>[10번째 턴 · 의사의 감별진단] 신경성 폭식증 (D022); 폭식장애 (D023)</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="B45" s="5" t="inlineStr">
+        <is>
+          <t>[11번째 턴 · 의사 질문] 이런 식사가 보통 아직 잠자리에 들기 전 저녁 시간에 일어나나요, 아니면 이미 잠자리에 들어 한동안 자고 난 후에 일어나나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="5" t="inlineStr">
+        <is>
+          <t>[11번째 턴 · 환자 응답] 솔직히 잘 모르겠어요. 잠들기 전인지 아니면 자고 난 후인지는 딱히 신경 써서 본 적이 없어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="B47" s="5" t="inlineStr">
+        <is>
+          <t>[11번째 턴 · 의사의 감별진단] 신경성 폭식증 (D022); 폭식장애 (D023)</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="B48" s="5" t="inlineStr">
+        <is>
+          <t>[12번째 턴 · 의사 질문] 아침에 식욕은 어떠세요? 보통 아침 식사가 하고 싶으신가요, 아니면 거르거나 아주 조금만 드시는 편인가요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="5" t="inlineStr">
+        <is>
+          <t>[12번째 턴 · 환자 응답] 잘 모르겠어요. 아침에 배가 고픈지, 아침을 얼마나 먹는지는 딱히 신경 써본 적이 없어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="B50" s="5" t="inlineStr">
+        <is>
+          <t>[12번째 턴 · 의사의 감별진단] 신경성 폭식증 (D022); 폭식장애 (D023)</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="B51" s="5" t="inlineStr">
+        <is>
+          <t>[13번째 턴 · 의사 질문] 이런 밤중 식사로 드시는 음식이 하루 전체 식사량 중에서 큰 부분을 차지한다고 보시나요? 아침, 점심, 저녁을 합친 것보다도 많을 정도로요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="5" t="inlineStr">
+        <is>
+          <t>[13번째 턴 · 환자 응답] 네, 아마 그럴 거예요. 거의 매일 밤 아내가 잠들고 나면 평소 식사량보다 훨씬 많이 먹어요. 프라이드치킨, 맥앤치즈, 고구마, 롤빵, 남은 건 뭐든지요. 어떨 때는 접시 하나를 다 비우거나 냉장고 절반을 먹어치워요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="B53" s="5" t="inlineStr">
+        <is>
+          <t>[13번째 턴 · 의사의 감별진단] 신경성 폭식증 (D022); 폭식장애 (D023)</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>최종 진단 및 진단 체크리스트</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="5" t="inlineStr">
         <is>
           <t>진단명: 폭식장애 (D023)
 인구통계: 성별 남성 / 나이 39 / 직업상태 not in workforce / 최종학력 대학 재학
@@ -575,350 +852,37 @@
 증상 지속 기간: 1 year and 2 months
 추가 요건: The binge eating occurs, on average, at least once a week for 3 months
 주호소 증상 코드: S049
-배경 서술: George와 그의 아내는 행사 계약이 오랫동안 끊기면서 대출금을 연체하게 되었고, 집에 대한 압류 절차가 진행되면서 그가 스스로 계획해서 헤쳐나갈 수 없었던 첫 위기가 되었다. 그는 평소 자신의 한 주를 짜임새 있게 만들어주던 지역사회 기획 활동 중 일부에서 손을 떼기 시작했다. 이후 1년 2개월에 걸쳐, 예전에는 다른 사람들을 위해 요리하던 저녁 시간이 배고프지도 않은데 소울푸드나 배달 음식, 행사에서 남은 음식을 빠르게, 아주 많은 양을 먹는 일이 반복되는 시간으로 바뀌었고, 부엌에 혼자 있을 때면 통제력을 잃은 듯한 느낌이 들었다. 그 여파는 점점 더 고통스러워졌는데, 활기차고 너그럽고 절제력 있는 사람이라는 그의 공적인 이미지와 상충하는 수치심, 죄책감, 자기혐오가 뒤따랐다. 그는 정기 검진에서 주치의에게 처음으로 이 패턴에 대해 이야기하고, 이것을 단순히 압류로 인한 스트레스로만 설명하기보다 진료 의뢰를 받아들이면서 정신건강의학과 진료를 받게 되었다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>대화문</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="B18" s="5" t="inlineStr">
-        <is>
-          <t>[1번째 턴 · 의사 질문] 안녕하세요, 어서 오세요. 저는 [Name] 선생님입니다. 먼저, 오늘 어떤 일로 오시게 되었는지 말씀해 주시겠어요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="5" t="inlineStr">
-        <is>
-          <t>[1번째 턴 · 환자 응답] 거의 매일 밤 아내가 잠자리에 들고 나면, 저는 부엌에서 평소 식사량보다 훨씬 많이 먹게 돼요. 프라이드치킨, 맥앤치즈, 고구마, 롤빵... 남은 게 뭐든 다요. 접시 하나가 다 비거나, 냉장고 절반이 빌 때까지 계속 먹어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="B20" s="5" t="inlineStr">
-        <is>
-          <t>[1번째 턴 · 의사의 감별진단] 중간확률: 신경성 폭식증 (D022); 폭식장애 (D023)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="B21" s="5" t="inlineStr">
-        <is>
-          <t>[2번째 턴 · 의사 질문] 밤에 그렇게 드실 때, 완전히 깨어 있고 본인이 뭘 하는지 알고 계신가요, 아니면 완전히 깨어 있지 않은 것 같고 나중에 그걸 명확히 기억하는 데 어려움이 있으신가요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="5" t="inlineStr">
-        <is>
-          <t>[2번째 턴 · 환자 응답] 무슨 말씀이신지 잘 모르겠어요. 제가 부엌에서 일어나 먹고 있다는 건 아는데, 얼마나 깨어 있는지는 딱히 신경 써본 적이 없어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="B23" s="5" t="inlineStr">
-        <is>
-          <t>[2번째 턴 · 의사의 감별진단] 중간확률: 신경성 폭식증 (D022); 폭식장애 (D023)</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="B24" s="5" t="inlineStr">
-        <is>
-          <t>[3번째 턴 · 의사 질문] 다음 날 아침에, 밤에 뭘 얼마나 먹었는지 명확히 기억하시나요, 아니면 누가 말해주거나 흔적을 보기 전까지는 거의, 혹은 전혀 기억이 안 나기도 하시나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="5" t="inlineStr">
-        <is>
-          <t>[3번째 턴 · 환자 응답] 솔직히 잘 모르겠어요. 다음 날 그걸 다 기억하는지는 별로 생각해본 적이 없어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="B26" s="5" t="inlineStr">
-        <is>
-          <t>[3번째 턴 · 의사의 감별진단] 중간확률: 신경성 폭식증 (D022); 폭식장애 (D023)</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="B27" s="5" t="inlineStr">
-        <is>
-          <t>[4번째 턴 · 의사 질문] 이런 일이 일어날 때, 의식적으로 깨어나서 부엌에 가기로 결정한 걸 기억하시나요, 아니면 어떻게 갔는지도 모른 채 어느새 부엌에서 먹고 있는 자신을 발견하시나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="5" t="inlineStr">
-        <is>
-          <t>[4번째 턴 · 환자 응답] 잘 모르겠어요. 제가 의식적으로 일어나기로 결정하는 건지 아닌지는 딱히 신경 써본 적이 없고, 그냥 정신 차려보면 부엌에서 먹고 있더라고요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="B29" s="5" t="inlineStr">
-        <is>
-          <t>[4번째 턴 · 의사의 감별진단] 중간확률: 신경성 폭식증 (D022); 폭식장애 (D023)</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="B30" s="5" t="inlineStr">
-        <is>
-          <t>[5번째 턴 · 의사 질문] 아내분이 이런 밤중 식사 중에 말을 걸거나 반응을 보려고 한 적이 있나요? 그렇다면, 완전히 깨어 있는 사람처럼 평소대로 반응하시나요, 아니면 혼란스러워 보이거나 반응이 없거나 '정신이 나가 있는' 것처럼 보이나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="5" t="inlineStr">
-        <is>
-          <t>[5번째 턴 · 환자 응답] 잘 모르겠어요. 그런 일이 일어나는 동안 아내가 저한테 말을 걸어본 적이 있는지에 대해서는 서로 얘기해본 적이 없어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="B32" s="5" t="inlineStr">
-        <is>
-          <t>[5번째 턴 · 의사의 감별진단] 중간확률: 신경성 폭식증 (D022); 폭식장애 (D023)</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="B33" s="5" t="inlineStr">
-        <is>
-          <t>[6번째 턴 · 의사 질문] 이럴 때, 낮에 완전히 깨어 있을 때처럼 부엌 불을 켜거나 접시와 식기를 사용하고 물건에 부딪히지 않고 다니실 수 있나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="5" t="inlineStr">
-        <is>
-          <t>[6번째 턴 · 환자 응답] 잘 모르겠어요. 그럴 때 그런 걸 평소대로 하고 있는지는 신경 써본 적이 없어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="B35" s="5" t="inlineStr">
-        <is>
-          <t>[6번째 턴 · 의사의 감별진단] 중간확률: 신경성 폭식증 (D022); 폭식장애 (D023)</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="B36" s="5" t="inlineStr">
-        <is>
-          <t>[7번째 턴 · 의사 질문] 이런 일이 일어나기 전에, 실제로 먼저 잠이 들었다가 먹으려고 깨어나시는 건가요, 아니면 아직 잠들지 않은 상태로 깨어 있다가 부엌에 가시는 건가요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="5" t="inlineStr">
-        <is>
-          <t>[7번째 턴 · 환자 응답] 솔직히 잘 모르겠어요. 부엌에 가기 전에 먼저 잠이 들었는지 아니면 계속 깨어 있었는지는 딱히 확인해본 적이 없어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="B38" s="5" t="inlineStr">
-        <is>
-          <t>[7번째 턴 · 의사의 감별진단] 중간확률: 신경성 폭식증 (D022); 폭식장애 (D023)</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="B39" s="5" t="inlineStr">
-        <is>
-          <t>[8번째 턴 · 의사 질문] 부엌에 가시기 전에, 배가 고파서 일어나 먹기로 선택하는 것처럼 의식적인 충동이나 식욕을 느끼시나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="5" t="inlineStr">
-        <is>
-          <t>[8번째 턴 · 환자 응답] 대부분은 아니에요, 딱히 배고프지 않아요. 아내랑 이미 저녁을 먹었을 수도 있는데, 그러고도 나중에 결국 부엌에서 남은 음식을 집어 먹다가 그게 또 한 끼가 되어버려요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="B41" s="5" t="inlineStr">
-        <is>
-          <t>[8번째 턴 · 의사의 감별진단] 중간확률: 신경성 폭식증 (D022); 폭식장애 (D023)</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="B42" s="5" t="inlineStr">
-        <is>
-          <t>[9번째 턴 · 의사 질문] 이런 밤중 식사 후에 감정적으로 어떤 기분이 드시나요? 속상하거나, 죄책감이 들거나, 창피하신가요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="5" t="inlineStr">
-        <is>
-          <t>[9번째 턴 · 환자 응답] 네. 끝나고 나면 제 자신이 역겨워요. 사람들은 저를 체계적이고 강한 사람으로 보는데, 저는 거기 앉아서 부끄럽고 죄책감이 들고, 또 이런 일이 일어나게 놔뒀다는 게 정말 혐오스러워요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="B44" s="5" t="inlineStr">
-        <is>
-          <t>[9번째 턴 · 의사의 감별진단] 중간확률: 신경성 폭식증 (D022); 폭식장애 (D023)</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="B45" s="5" t="inlineStr">
-        <is>
-          <t>[10번째 턴 · 의사 질문] 혹시 잠에서 깼을 때 부엌에 접시나 포장지, 음식이 나와 있는데 그걸 준비했거나 먹었던 기억이 전혀 없었던 적이 있나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="5" t="inlineStr">
-        <is>
-          <t>[10번째 턴 · 환자 응답] 모르겠어요. 그런 걸 본 적은 없는데, 딱히 확인해본 적도 없어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="B47" s="5" t="inlineStr">
-        <is>
-          <t>[10번째 턴 · 의사의 감별진단] 중간확률: 신경성 폭식증 (D022); 폭식장애 (D023)</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="B48" s="5" t="inlineStr">
-        <is>
-          <t>[11번째 턴 · 의사 질문] 이런 식사가 보통 아직 잠자리에 들기 전 저녁 시간에 일어나나요, 아니면 이미 잠자리에 들어 한동안 자고 난 후에 일어나나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="5" t="inlineStr">
-        <is>
-          <t>[11번째 턴 · 환자 응답] 솔직히 잘 모르겠어요. 잠들기 전인지 아니면 자고 난 후인지는 딱히 신경 써서 본 적이 없어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="B50" s="5" t="inlineStr">
-        <is>
-          <t>[11번째 턴 · 의사의 감별진단] 중간확률: 신경성 폭식증 (D022); 폭식장애 (D023)</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="B51" s="5" t="inlineStr">
-        <is>
-          <t>[12번째 턴 · 의사 질문] 아침에 식욕은 어떠세요? 보통 아침 식사가 하고 싶으신가요, 아니면 거르거나 아주 조금만 드시는 편인가요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="5" t="inlineStr">
-        <is>
-          <t>[12번째 턴 · 환자 응답] 잘 모르겠어요. 아침에 배가 고픈지, 아침을 얼마나 먹는지는 딱히 신경 써본 적이 없어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="B53" s="5" t="inlineStr">
-        <is>
-          <t>[12번째 턴 · 의사의 감별진단] 중간확률: 신경성 폭식증 (D022); 폭식장애 (D023)</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="B54" s="5" t="inlineStr">
-        <is>
-          <t>[13번째 턴 · 의사 질문] 이런 밤중 식사로 드시는 음식이 하루 전체 식사량 중에서 큰 부분을 차지한다고 보시나요? 아침, 점심, 저녁을 합친 것보다도 많을 정도로요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="5" t="inlineStr">
-        <is>
-          <t>[13번째 턴 · 환자 응답] 네, 아마 그럴 거예요. 거의 매일 밤 아내가 잠들고 나면 평소 식사량보다 훨씬 많이 먹어요. 프라이드치킨, 맥앤치즈, 고구마, 롤빵, 남은 건 뭐든지요. 어떨 때는 접시 하나를 다 비우거나 냉장고 절반을 먹어치워요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
+배경 서술: George와 그의 아내는 행사 계약이 오랫동안 끊기면서 대출금을 연체하게 되었고, 집에 대한 압류 절차가 진행되면서 그가 스스로 계획해서 헤쳐나갈 수 없었던 첫 위기가 되었다. 그는 평소 자신의 한 주를 짜임새 있게 만들어주던 지역사회 기획 활동 중 일부에서 손을 떼기 시작했다. 이후 1년 2개월에 걸쳐, 예전에는 다른 사람들을 위해 요리하던 저녁 시간이 배고프지도 않은데 소울푸드나 배달 음식, 행사에서 남은 음식을 빠르게, 아주 많은 양을 먹는 일이 반복되는 시간으로 바뀌었고, 부엌에 혼자 있을 때면 통제력을 잃은 듯한 느낌이 들었다. 그 여파는 점점 더 고통스러워졌는데, 활기차고 너그럽고 절제력 있는 사람이라는 그의 공적인 이미지와 상충하는 수치심, 죄책감, 자기혐오가 뒤따랐다. 그는 정기 검진에서 주치의에게 처음으로 이 패턴에 대해 이야기하고, 이것을 단순히 압류로 인한 스트레스로만 설명하기보다 진료 의뢰를 받아들이면서 정신건강의학과 진료를 받게 되었다.
+표집된 증상 목록:
+  - S049 대량 섭취: 일정 시간 동안 대부분의 사람이 비슷한 상황에서 먹는 양보다 명백히 많은 양을 먹음.
+  - S050 조절 상실감: 먹는 동안 스스로 통제할 수 없다는 느낌(예: 먹는 것을 멈출 수 없거나 무엇을, 얼마나 먹는지 조절할 수 없다는 느낌).
+  - S051 급하게 먹기: 평소보다 훨씬 빠르게 먹음.
+  - S053 배고프지 않은데 먹기: 신체적으로 배고프지 않은데도 많은 양의 음식을 먹음.
+  - S055 폭식 후 부정적 정서: 폭식 후 스스로에게 혐오감을 느끼거나 우울해지거나 심한 죄책감을 느낌.</t>
+        </is>
+      </c>
       <c r="B56" s="5" t="inlineStr">
         <is>
-          <t>[13번째 턴 · 의사의 감별진단] 중간확률: 신경성 폭식증 (D022); 폭식장애 (D023)</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="2" t="inlineStr">
-        <is>
-          <t>최종 진단 및 진단 체크리스트</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="6" t="inlineStr">
-        <is>
-          <t>의사의 최종 진단: 폭식장애 (D023, ICD: F50.8)</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="5" t="inlineStr">
-        <is>
-          <t>지속 기간 요건 — 점수: 0.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="5" t="inlineStr">
-        <is>
-          <t>기능적 손상 요건 — 점수: None</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="5" t="inlineStr">
-        <is>
-          <t>추가 요건 — 점수: 0.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="5" t="inlineStr">
-        <is>
-          <t>체크리스트 그룹: binge_episode (관계=must_include, 요구개수=2, 충족개수=1, 커버리지=0.5)
-  확인된 근거: 대량 섭취: 일정 시간 동안 대부분의 사람이 비슷한 상황에서 먹는 양보다 명백히 많은 양을 먹음.
-  누락: 조절 상실감: 먹는 동안 스스로 통제할 수 없다는 느낌(예: 먹는 것을 멈출 수 없거나 무엇을, 얼마나 먹는지 조절할 수 없다는 느낌).</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="5" t="inlineStr">
-        <is>
-          <t>체크리스트 그룹: binge_episode_related (관계=must_include, 요구개수=3, 충족개수=2, 커버리지=0.6667)
-  확인된 근거: 배고프지 않은데 먹기: 신체적으로 배고프지 않은데도 많은 양의 음식을 먹음.; 폭식 후 부정적 정서: 폭식 후 스스로에게 혐오감을 느끼거나 우울해지거나 심한 죄책감을 느낌.
-  누락: 급하게 먹기: 평소보다 훨씬 빠르게 먹음.; 불편할 정도로 배부르게 먹기: 불편할 정도로 배가 부를 때까지 먹음.; 부끄러움으로 인한 혼자 먹기: 먹는 양이 부끄러워 혼자 먹음.</t>
+          <t>의사의 최종 진단: 폭식장애 (D023, ICD: F50.8)
+지속 기간 요건: 없음
+기능적 손상 요건: None
+추가 요건: 없음
+체크리스트 그룹: binge_episode (관계=must_include, 요구개수=2, 충족개수=1, 커버리지=0.5)
+확인된 근거:
+  - 대량 섭취: 일정 시간 동안 대부분의 사람이 비슷한 상황에서 먹는 양보다 명백히 많은 양을 먹음.
+체크리스트 그룹: binge_episode_related (관계=must_include, 요구개수=3, 충족개수=2, 커버리지=0.6667)
+확인된 근거:
+  - 배고프지 않은데 먹기: 신체적으로 배고프지 않은데도 많은 양의 음식을 먹음.
+  - 폭식 후 부정적 정서: 폭식 후 스스로에게 혐오감을 느끼거나 우울해지거나 심한 죄책감을 느낌.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="4">
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="A3:B3"/>
     <mergeCell ref="A14:B14"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="A58:B58"/>
+    <mergeCell ref="A55:B55"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/human_validation/judge/kor/judge_D023_S001_P002__claude-sonnet-5_kor.xlsx
+++ b/human_validation/judge/kor/judge_D023_S001_P002__claude-sonnet-5_kor.xlsx
@@ -838,6 +838,11 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
+          <t>환자 증상 프로필</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
           <t>최종 진단 및 진단 체크리스트</t>
         </is>
       </c>
@@ -878,11 +883,10 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="4">
+  <mergeCells count="3">
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="A3:B3"/>
     <mergeCell ref="A14:B14"/>
-    <mergeCell ref="A55:B55"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/human_validation/judge/kor/judge_D023_S001_P002__claude-sonnet-5_kor.xlsx
+++ b/human_validation/judge/kor/judge_D023_S001_P002__claude-sonnet-5_kor.xlsx
@@ -458,6 +458,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -502,7 +503,7 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="8">
@@ -555,6 +556,7 @@
         <v>0</v>
       </c>
     </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
